--- a/experimentacion_alpha.xlsx
+++ b/experimentacion_alpha.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="21">
   <si>
     <t xml:space="preserve">INITIAL_TEMPERATURE=1000 COOLING_RATE=0.95 MAX_ITERATIONS=1000000 COOLING_INTERVAL=50 MAX_STAGNATION=5000 SEED=42</t>
   </si>
@@ -31,6 +31,9 @@
     <t xml:space="preserve">(25) C101</t>
   </si>
   <si>
+    <t xml:space="preserve">SEED=42</t>
+  </si>
+  <si>
     <t xml:space="preserve">ALPHA</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
   </si>
   <si>
     <t xml:space="preserve">(100) C101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEED=24</t>
   </si>
   <si>
     <t xml:space="preserve">(400) c1_4_1</t>
@@ -158,7 +164,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -168,6 +174,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -302,7 +312,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F95"/>
+  <dimension ref="B2:G95"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.88"/>
@@ -323,22 +333,25 @@
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -357,6 +370,7 @@
       <c r="F7" s="2" t="n">
         <v>141.039</v>
       </c>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="n">
@@ -482,24 +496,27 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -507,16 +524,16 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>1275.96</v>
+        <v>1226.69</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>58253</v>
+        <v>57885.9</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>1275.96</v>
+        <v>1226.69</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -524,16 +541,16 @@
         <v>0.25</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>1361.71</v>
+        <v>1540.01</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>48.8076</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>1349.51</v>
+        <v>1540.01</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -541,16 +558,16 @@
         <v>0.5</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>1475.87</v>
+        <v>1817.22</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>0</v>
+        <v>3.45906</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>1475.87</v>
+        <v>1815.49</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -558,16 +575,16 @@
         <v>0.75</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>1481.79</v>
+        <v>1447.02</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>2.8304</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>1479.66</v>
+        <v>1447.02</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -575,7 +592,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>1766.31</v>
+        <v>1292.84</v>
       </c>
       <c r="D24" s="1" t="n">
         <v>0</v>
@@ -584,7 +601,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>1766.31</v>
+        <v>1292.84</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -592,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>1509.18</v>
+        <v>1332.85</v>
       </c>
       <c r="D25" s="1" t="n">
         <v>0</v>
@@ -601,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>1509.18</v>
+        <v>1332.85</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -609,7 +626,7 @@
         <v>5</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>1715.88</v>
+        <v>1489.56</v>
       </c>
       <c r="D26" s="1" t="n">
         <v>0</v>
@@ -618,7 +635,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>1715.88</v>
+        <v>1489.56</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -626,16 +643,16 @@
         <v>10</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>1763.81</v>
+        <v>1344.23</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>0</v>
+        <v>0.80464</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>1763.81</v>
+        <v>1336.18</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -643,24 +660,24 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -804,24 +821,24 @@
         <v>1</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -965,30 +982,30 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1081,30 +1098,30 @@
         <v>1</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1125,7 +1142,7 @@
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="3" t="n">
+      <c r="B69" s="4" t="n">
         <v>0.97</v>
       </c>
       <c r="C69" s="1" t="n">
@@ -1142,7 +1159,7 @@
       </c>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="3" t="n">
+      <c r="B70" s="4" t="n">
         <v>0.98</v>
       </c>
       <c r="C70" s="1" t="n">
@@ -1159,7 +1176,7 @@
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="3" t="n">
+      <c r="B71" s="4" t="n">
         <v>0.99</v>
       </c>
       <c r="C71" s="1" t="n">
@@ -1176,7 +1193,7 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="3" t="n">
+      <c r="B72" s="4" t="n">
         <v>0.995</v>
       </c>
       <c r="C72" s="1" t="n">
@@ -1197,30 +1214,30 @@
         <v>1</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1344,27 +1361,27 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1380,7 +1397,7 @@
       <c r="E89" s="1" t="n">
         <v>26412.4</v>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F89" s="5" t="n">
         <v>424.399</v>
       </c>
     </row>

--- a/experimentacion_alpha.xlsx
+++ b/experimentacion_alpha.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="26">
   <si>
     <t xml:space="preserve">INITIAL_TEMPERATURE=1000 COOLING_RATE=0.95 MAX_ITERATIONS=1000000 COOLING_INTERVAL=50 MAX_STAGNATION=5000 SEED=42</t>
   </si>
@@ -31,36 +31,51 @@
     <t xml:space="preserve">(25) C101</t>
   </si>
   <si>
+    <t xml:space="preserve">SEED=16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALPHA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor objetivo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nodos penalizados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penalización de tiempo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distancia total recorrida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiempo (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(100) C101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEED=24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(200) C1-2-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEED=36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(400) c1_4_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEED=32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(1000) c1_4_1</t>
+  </si>
+  <si>
     <t xml:space="preserve">SEED=42</t>
   </si>
   <si>
-    <t xml:space="preserve">ALPHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valor objetivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nodos penalizados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penalización de tiempo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distancia total recorrida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(100) C101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEED=24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(400) c1_4_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(1000) c1_4_1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alpha=1</t>
   </si>
   <si>
@@ -79,18 +94,19 @@
     <t xml:space="preserve">max_stagnation</t>
   </si>
   <si>
-    <t xml:space="preserve"> C101(50)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">make run ALPHA=0.25 INITIAL_TEMPERATURE=5000 COOLING_RATE=0.98 MAX_ITERATIONS=1000000 COOLING_INTERVAL=50 MAX_STAGNATION=20000 SEED=42</t>
+    <t xml:space="preserve">SEED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(200) c1_ 2 _ 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -164,7 +180,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -177,7 +193,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -312,7 +332,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G95"/>
+  <dimension ref="B2:G144"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.88"/>
@@ -353,40 +373,48 @@
       <c r="F6" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="G6" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>141.039</v>
+        <v>145.201</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>19</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>12289.9</v>
+        <v>9767.63</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>141.039</v>
-      </c>
-      <c r="G7" s="3"/>
+        <v>145.201</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>3.71485</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="n">
         <v>0.25</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>213.568</v>
+        <v>162.577</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>10.6011</v>
+        <v>0</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>210.918</v>
+        <v>162.577</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3.86379</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -405,13 +433,16 @@
       <c r="F9" s="1" t="n">
         <v>162.577</v>
       </c>
+      <c r="G9" s="4" t="n">
+        <v>3.84458</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="n">
         <v>0.75</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>174.17</v>
+        <v>233.531</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>0</v>
@@ -420,7 +451,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>174.17</v>
+        <v>233.531</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>3.7414</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -428,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>182.328</v>
+        <v>162.577</v>
       </c>
       <c r="D11" s="1" t="n">
         <v>0</v>
@@ -437,7 +471,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>182.328</v>
+        <v>162.577</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>3.9023</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -445,7 +482,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>217.064</v>
+        <v>162.577</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>0</v>
@@ -454,7 +491,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>217.064</v>
+        <v>162.577</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>3.81142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -462,7 +502,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>210.982</v>
+        <v>283.036</v>
       </c>
       <c r="D13" s="1" t="n">
         <v>0</v>
@@ -471,7 +511,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>210.982</v>
+        <v>283.036</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>3.82113</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -479,7 +522,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>162.577</v>
+        <v>213.249</v>
       </c>
       <c r="D14" s="1" t="n">
         <v>0</v>
@@ -488,7 +531,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>162.577</v>
+        <v>213.249</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>3.88926</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -496,10 +542,10 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -518,6 +564,9 @@
       <c r="F19" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="G19" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="n">
@@ -534,6 +583,9 @@
       </c>
       <c r="F20" s="1" t="n">
         <v>1226.69</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>10.6077</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -552,6 +604,9 @@
       <c r="F21" s="1" t="n">
         <v>1540.01</v>
       </c>
+      <c r="G21" s="4" t="n">
+        <v>13.0905</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="n">
@@ -569,6 +624,9 @@
       <c r="F22" s="1" t="n">
         <v>1815.49</v>
       </c>
+      <c r="G22" s="4" t="n">
+        <v>13.2322</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="n">
@@ -586,6 +644,9 @@
       <c r="F23" s="1" t="n">
         <v>1447.02</v>
       </c>
+      <c r="G23" s="4" t="n">
+        <v>13.0595</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="n">
@@ -602,6 +663,9 @@
       </c>
       <c r="F24" s="1" t="n">
         <v>1292.84</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>12.8931</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -620,6 +684,9 @@
       <c r="F25" s="1" t="n">
         <v>1332.85</v>
       </c>
+      <c r="G25" s="4" t="n">
+        <v>12.8417</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="n">
@@ -637,6 +704,9 @@
       <c r="F26" s="1" t="n">
         <v>1489.56</v>
       </c>
+      <c r="G26" s="4" t="n">
+        <v>12.9129</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="n">
@@ -654,13 +724,19 @@
       <c r="F27" s="1" t="n">
         <v>1336.18</v>
       </c>
+      <c r="G27" s="4" t="n">
+        <v>13.0112</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -679,828 +755,1700 @@
       <c r="F31" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="G31" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>12027.9</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>305</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>227413</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>12027.9</v>
+      <c r="B32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>3954.04</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>155</v>
+      </c>
+      <c r="E32" s="0" t="n">
+        <v>130070</v>
+      </c>
+      <c r="F32" s="0" t="n">
+        <v>3954.04</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>18.0013</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="0" t="n">
         <v>0.25</v>
       </c>
-      <c r="C33" s="1" t="n">
-        <v>15145.4</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>991.255</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>14897.6</v>
+      <c r="C33" s="0" t="n">
+        <v>5830.37</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="E33" s="0" t="n">
+        <v>422.539</v>
+      </c>
+      <c r="F33" s="0" t="n">
+        <v>5724.73</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>22.2574</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="C34" s="1" t="n">
-        <v>16526.3</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>544.306</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>16254.2</v>
+      <c r="C34" s="0" t="n">
+        <v>6225.42</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="E34" s="0" t="n">
+        <v>218.416</v>
+      </c>
+      <c r="F34" s="0" t="n">
+        <v>6116.21</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>21.9013</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="0" t="n">
         <v>0.75</v>
       </c>
-      <c r="C35" s="1" t="n">
-        <v>16557.6</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>522.069</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>16166</v>
+      <c r="C35" s="0" t="n">
+        <v>6384.64</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" s="0" t="n">
+        <v>199.08</v>
+      </c>
+      <c r="F35" s="0" t="n">
+        <v>6235.33</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>21.8849</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>15618.3</v>
-      </c>
-      <c r="D36" s="1" t="n">
+      <c r="B36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>5241.16</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="0" t="n">
+        <v>62.1973</v>
+      </c>
+      <c r="F36" s="0" t="n">
+        <v>5178.96</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>21.1336</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>6145.43</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="0" t="n">
+        <v>6145.43</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>21.3549</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>7319.22</v>
+      </c>
+      <c r="D38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="0" t="n">
+        <v>11.9016</v>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>7259.71</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>21.9098</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>6004.93</v>
+      </c>
+      <c r="D39" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="0" t="n">
+        <v>5.33372</v>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>5951.6</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>21.054</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="0"/>
+      <c r="D40" s="0"/>
+      <c r="E40" s="0"/>
+      <c r="F40" s="0"/>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C41" s="0"/>
+      <c r="D41" s="0"/>
+      <c r="E41" s="0"/>
+      <c r="F41" s="0"/>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="0" t="s">
         <v>9</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>117.957</v>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>15500.4</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>18807.5</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>18.827</v>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>18751.1</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>17690.8</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1" t="n">
-        <v>0.511386</v>
-      </c>
-      <c r="F38" s="1" t="n">
-        <v>17688.3</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>18328.5</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="1" t="n">
-        <v>11.5043</v>
-      </c>
-      <c r="F39" s="1" t="n">
-        <v>18213.4</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>65513.9</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>808</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>751213</v>
-      </c>
-      <c r="F44" s="1" t="n">
-        <v>65513.9</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="1" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>90132.6</v>
+        <v>12072.1</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>201</v>
+        <v>308</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>16925.8</v>
+        <v>227800</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>85901.2</v>
+        <v>12072.1</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>32.3001</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="1" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>110302</v>
+        <v>13972.8</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>150</v>
+        <v>31</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>8512.76</v>
+        <v>1024.33</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>106046</v>
+        <v>13716.7</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>42.3189</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>114916</v>
+        <v>17807.9</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>6491.03</v>
+        <v>545.966</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>110047</v>
+        <v>17534.9</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>44.937</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="1" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>101571</v>
+        <v>17033.3</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>3756.61</v>
+        <v>243.998</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>97814.6</v>
+        <v>16850.3</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>46.0276</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>121151</v>
+        <v>20541.5</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>780.884</v>
+        <v>347.024</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>118808</v>
+        <v>20194.4</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>47.3253</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="1" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>128280</v>
+        <v>17433.4</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>651.157</v>
+        <v>25.6175</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>125024</v>
+        <v>17356.5</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>45.4308</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>19661</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>10.3776</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>19609.1</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>49.3745</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C51" s="1" t="n">
-        <v>129886</v>
-      </c>
-      <c r="D51" s="1" t="n">
+      <c r="C52" s="1" t="n">
+        <v>18570.1</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>18570.1</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>46.4718</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E51" s="1" t="n">
-        <v>398.82</v>
-      </c>
-      <c r="F51" s="1" t="n">
-        <v>125898</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G56" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>65513.9</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>808</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>751213</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>65513.9</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>55.3599</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>8</v>
+      <c r="B58" s="1" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>90132.6</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>16925.8</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>85901.2</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>101.821</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="1" t="n">
-        <v>100</v>
+        <v>0.5</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>17088.6</v>
+        <v>110302</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>183.465</v>
+        <v>8512.76</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>16905.2</v>
+        <v>106046</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>117.23</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="1" t="n">
-        <v>500</v>
+        <v>0.75</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>18108.8</v>
+        <v>114916</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>11</v>
+        <v>150</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>253.658</v>
+        <v>6491.03</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>17855.1</v>
+        <v>110047</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>116.69</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="1" t="n">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>18112.3</v>
+        <v>101571</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>176.911</v>
+        <v>3756.61</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>17935.4</v>
+        <v>97814.6</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>115.655</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="1" t="n">
-        <v>5000</v>
+        <v>3</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>16022.8</v>
+        <v>121151</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>82.1674</v>
+        <v>780.884</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>15940.6</v>
+        <v>118808</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>121.698</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>128280</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>651.157</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>125024</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>125.817</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>129886</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>398.82</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>125898</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>119.143</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>17088.6</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>183.465</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>16905.2</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>18108.8</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>253.658</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>17855.1</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>18112.3</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>176.911</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>17935.4</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>16022.8</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>82.1674</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>15940.6</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="1" t="n">
         <v>10000</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C76" s="1" t="n">
         <v>17445.3</v>
       </c>
-      <c r="D63" s="1" t="n">
+      <c r="D76" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="E63" s="1" t="n">
+      <c r="E76" s="1" t="n">
         <v>196.747</v>
       </c>
-      <c r="F63" s="1" t="n">
+      <c r="F76" s="1" t="n">
         <v>17248.5</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E65" s="1" t="s">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" s="1" t="s">
+      <c r="D78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C80" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D80" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E80" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F80" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="1" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C68" s="1" t="n">
-        <v>17321.4</v>
-      </c>
-      <c r="D68" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E68" s="1" t="n">
-        <v>103.058</v>
-      </c>
-      <c r="F68" s="1" t="n">
-        <v>17218.3</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="4" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>17360.2</v>
-      </c>
-      <c r="D69" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="E69" s="1" t="n">
-        <v>184.298</v>
-      </c>
-      <c r="F69" s="1" t="n">
-        <v>17175.9</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>14271</v>
-      </c>
-      <c r="D70" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E70" s="1" t="n">
-        <v>219.675</v>
-      </c>
-      <c r="F70" s="1" t="n">
-        <v>14051.3</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="4" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>16022.8</v>
-      </c>
-      <c r="D71" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="E71" s="1" t="n">
-        <v>82.1674</v>
-      </c>
-      <c r="F71" s="1" t="n">
-        <v>15940.6</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="4" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>17976.5</v>
-      </c>
-      <c r="D72" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E72" s="1" t="n">
-        <v>316.084</v>
-      </c>
-      <c r="F72" s="1" t="n">
-        <v>17660.4</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C77" s="1" t="n">
-        <v>26245.7</v>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>744.137</v>
-      </c>
-      <c r="F77" s="1" t="n">
-        <v>25501.5</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="1" t="n">
-        <v>2500</v>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>18621.3</v>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>411.262</v>
-      </c>
-      <c r="F78" s="1" t="n">
-        <v>18210</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="1" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C79" s="1" t="n">
-        <v>14271</v>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="E79" s="1" t="n">
-        <v>219.675</v>
-      </c>
-      <c r="F79" s="1" t="n">
-        <v>14051.3</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="1" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>13410.7</v>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>41.2605</v>
-      </c>
-      <c r="F80" s="1" t="n">
-        <v>13369.4</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="1" t="n">
-        <v>15000</v>
+        <v>0.95</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>11965.3</v>
+        <v>17321.4</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>33.4986</v>
+        <v>103.058</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>11931.8</v>
+        <v>17218.3</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="1" t="n">
-        <v>20000</v>
+      <c r="B82" s="5" t="n">
+        <v>0.97</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>11175.8</v>
+        <v>17360.2</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>12.1153</v>
+        <v>184.298</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>11163.6</v>
+        <v>17175.9</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="1" t="n">
-        <v>30000</v>
+      <c r="B83" s="5" t="n">
+        <v>0.98</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>11175.8</v>
+        <v>14271</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>12.1153</v>
+        <v>219.675</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>11163.6</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="1" t="s">
+        <v>14051.3</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>16022.8</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>82.1674</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>15940.6</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="5" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>17976.5</v>
+      </c>
+      <c r="D85" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C88" s="1" t="s">
+      <c r="E85" s="1" t="n">
+        <v>316.084</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>17660.4</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E88" s="1" t="s">
+      <c r="E89" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F89" s="1" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="1" t="n">
-        <v>424.399</v>
-      </c>
-      <c r="D89" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="E89" s="1" t="n">
-        <v>26412.4</v>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>424.399</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="1" t="n">
-        <v>0.25</v>
+        <v>1000</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>483.326</v>
+        <v>26245.7</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>0</v>
+        <v>744.137</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>483.326</v>
+        <v>25501.5</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="1" t="n">
-        <v>0.5</v>
+        <v>2500</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>466.7</v>
+        <v>18621.3</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>0</v>
+        <v>411.262</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>466.7</v>
+        <v>18210</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="1" t="n">
-        <v>0.75</v>
+        <v>5000</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>463.09</v>
+        <v>14271</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>0</v>
+        <v>219.675</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>463.09</v>
+        <v>14051.3</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="1" t="n">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>516.213</v>
+        <v>13410.7</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>0</v>
+        <v>41.2605</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>516.213</v>
+        <v>13369.4</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>11965.3</v>
+      </c>
+      <c r="D94" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C94" s="1" t="n">
-        <v>549.72</v>
-      </c>
-      <c r="D94" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="E94" s="1" t="n">
-        <v>0</v>
+        <v>33.4986</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>549.72</v>
+        <v>11931.8</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="1" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>11175.8</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>12.1153</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>11163.6</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="1" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>11175.8</v>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>12.1153</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>11163.6</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C101" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C95" s="1" t="n">
-        <v>511.818</v>
-      </c>
-      <c r="D95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="1" t="n">
-        <v>511.818</v>
+      <c r="D101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>11270.4</v>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>19.2888</v>
+      </c>
+      <c r="F102" s="6" t="n">
+        <v>11251.1</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>32.696</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>12154.6</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>92.8082</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>12061.8</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>31.6937</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>12119.5</v>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>74.1605</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>12045.3</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>33.3119</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>13511.5</v>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>92.9482</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>13418.6</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>31.9868</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>12358.5</v>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>64.3894</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>12294.1</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>31.064</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C107" s="0" t="n">
+        <f aca="false">AVERAGE(C102:C106)</f>
+        <v>12282.9</v>
+      </c>
+      <c r="D107" s="0"/>
+      <c r="E107" s="0"/>
+      <c r="F107" s="0"/>
+      <c r="G107" s="4" t="n">
+        <f aca="false">AVERAGE(G102:G106)</f>
+        <v>32.15048</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C108" s="4" t="n">
+        <f aca="false">_xlfn.STDEV.S(C102:C106)</f>
+        <v>803.661934522222</v>
+      </c>
+      <c r="D108" s="0"/>
+      <c r="E108" s="0"/>
+      <c r="F108" s="0"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" s="0"/>
+      <c r="E109" s="0"/>
+      <c r="F109" s="0"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G110" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C111" s="0" t="n">
+        <v>101984</v>
+      </c>
+      <c r="D111" s="0" t="n">
+        <v>84</v>
+      </c>
+      <c r="E111" s="0" t="n">
+        <v>2862.14</v>
+      </c>
+      <c r="F111" s="0" t="n">
+        <v>99121.9</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>83.7511</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C112" s="0" t="n">
+        <v>98313.6</v>
+      </c>
+      <c r="D112" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="E112" s="0" t="n">
+        <v>3419.08</v>
+      </c>
+      <c r="F112" s="0" t="n">
+        <v>94894.5</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>83.33</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C113" s="0" t="n">
+        <v>95470.3</v>
+      </c>
+      <c r="D113" s="0" t="n">
+        <v>89</v>
+      </c>
+      <c r="E113" s="0" t="n">
+        <v>3034.71</v>
+      </c>
+      <c r="F113" s="0" t="n">
+        <v>92435.6</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>86.7559</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C114" s="0" t="n">
+        <v>99769.9</v>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>98</v>
+      </c>
+      <c r="E114" s="0" t="n">
+        <v>3569.21</v>
+      </c>
+      <c r="F114" s="0" t="n">
+        <v>96200.7</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>83.4396</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C115" s="0" t="n">
+        <v>97002.4</v>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="E115" s="0" t="n">
+        <v>2780.07</v>
+      </c>
+      <c r="F115" s="0" t="n">
+        <v>94222.4</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>82.9972</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C116" s="0" t="n">
+        <f aca="false">AVERAGE(C111:C115)</f>
+        <v>98508.04</v>
+      </c>
+      <c r="D116" s="0"/>
+      <c r="E116" s="0"/>
+      <c r="F116" s="0"/>
+      <c r="G116" s="4" t="n">
+        <f aca="false">AVERAGE(G111:G115)</f>
+        <v>84.05476</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C117" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.S(C111:C115)</f>
+        <v>2510.33920078542</v>
+      </c>
+      <c r="D117" s="0"/>
+      <c r="E117" s="0"/>
+      <c r="F117" s="0"/>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D118" s="0"/>
+      <c r="E118" s="0"/>
+      <c r="F118" s="0"/>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G119" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C120" s="0" t="n">
+        <v>3623.13</v>
+      </c>
+      <c r="D120" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="0" t="n">
+        <v>3.30281</v>
+      </c>
+      <c r="F120" s="0" t="n">
+        <v>3619.83</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>16.2618</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C121" s="0" t="n">
+        <v>4109.81</v>
+      </c>
+      <c r="D121" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" s="0" t="n">
+        <v>20.3315</v>
+      </c>
+      <c r="F121" s="0" t="n">
+        <v>4089.48</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>19.7838</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C122" s="0" t="n">
+        <v>4162.19</v>
+      </c>
+      <c r="D122" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E122" s="0" t="n">
+        <v>30.1293</v>
+      </c>
+      <c r="F122" s="0" t="n">
+        <v>4132.06</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>19.6927</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C123" s="0" t="n">
+        <v>4910.68</v>
+      </c>
+      <c r="D123" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="E123" s="0" t="n">
+        <v>32.4241</v>
+      </c>
+      <c r="F123" s="0" t="n">
+        <v>4878.25</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>21.3299</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C124" s="0" t="n">
+        <v>4457.48</v>
+      </c>
+      <c r="D124" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" s="0" t="n">
+        <v>9.36068</v>
+      </c>
+      <c r="F124" s="0" t="n">
+        <v>4448.12</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>21.4121</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C125" s="0" t="n">
+        <f aca="false">AVERAGE(C120:C124)</f>
+        <v>4252.658</v>
+      </c>
+      <c r="D125" s="0"/>
+      <c r="E125" s="0"/>
+      <c r="F125" s="0"/>
+      <c r="G125" s="4" t="n">
+        <f aca="false">AVERAGE(G120:G124)</f>
+        <v>19.69606</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C126" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.S(C120:C124)</f>
+        <v>474.299619723651</v>
+      </c>
+      <c r="D126" s="0"/>
+      <c r="E126" s="0"/>
+      <c r="F126" s="0"/>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="0"/>
+      <c r="E127" s="0"/>
+      <c r="F127" s="0"/>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G128" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C129" s="0" t="n">
+        <v>1199.56</v>
+      </c>
+      <c r="D129" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="0" t="n">
+        <v>0.903106</v>
+      </c>
+      <c r="F129" s="0" t="n">
+        <v>1198.66</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>12.435</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C130" s="0" t="n">
+        <v>1174.65</v>
+      </c>
+      <c r="D130" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" s="0" t="n">
+        <v>2.60786</v>
+      </c>
+      <c r="F130" s="0" t="n">
+        <v>1172.04</v>
+      </c>
+      <c r="G130" s="4" t="n">
+        <v>12.4806</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C131" s="0" t="n">
+        <v>1265.03</v>
+      </c>
+      <c r="D131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="0" t="n">
+        <v>1265.03</v>
+      </c>
+      <c r="G131" s="4" t="n">
+        <v>12.1866</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C132" s="0" t="n">
+        <v>1220.5</v>
+      </c>
+      <c r="D132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="0" t="n">
+        <v>1220.5</v>
+      </c>
+      <c r="G132" s="4" t="n">
+        <v>11.8561</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C133" s="0" t="n">
+        <v>1541.43</v>
+      </c>
+      <c r="D133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="0" t="n">
+        <v>1541.43</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>12.7362</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C134" s="0" t="n">
+        <f aca="false">AVERAGE(C129:C133)</f>
+        <v>1280.234</v>
+      </c>
+      <c r="D134" s="0"/>
+      <c r="E134" s="0"/>
+      <c r="F134" s="0"/>
+      <c r="G134" s="4" t="n">
+        <f aca="false">AVERAGE(G129:G133)</f>
+        <v>12.3389</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C135" s="0" t="n">
+        <f aca="false">_xlfn.STDEV.S(C129:C133)</f>
+        <v>149.732209393971</v>
+      </c>
+      <c r="D135" s="0"/>
+      <c r="E135" s="0"/>
+      <c r="F135" s="0"/>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D136" s="0"/>
+      <c r="E136" s="0"/>
+      <c r="F136" s="0"/>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G137" s="0" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="C138" s="0" t="n">
+        <v>229.63</v>
+      </c>
+      <c r="D138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" s="0" t="n">
+        <v>229.63</v>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>3.75825</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B139" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>155.936</v>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="0" t="n">
+        <v>155.936</v>
+      </c>
+      <c r="G139" s="4" t="n">
+        <v>3.82074</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>155.936</v>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" s="0" t="n">
+        <v>155.936</v>
+      </c>
+      <c r="G140" s="4" t="n">
+        <v>3.66526</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B141" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>229.63</v>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="0" t="n">
+        <v>229.63</v>
+      </c>
+      <c r="G141" s="4" t="n">
+        <v>3.81743</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>162.577</v>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F142" s="0" t="n">
+        <v>162.577</v>
+      </c>
+      <c r="G142" s="4" t="n">
+        <v>3.80633</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C143" s="1" t="n">
+        <f aca="false">AVERAGE(C138:C142)</f>
+        <v>186.7418</v>
+      </c>
+      <c r="G143" s="4" t="n">
+        <f aca="false">AVERAGE(G138:G142)</f>
+        <v>3.773602</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C144" s="1" t="n">
+        <f aca="false">_xlfn.STDEV.S(C138:C142)</f>
+        <v>39.2451512444531</v>
       </c>
     </row>
   </sheetData>
